--- a/tabelas_classes_excel/Tabela_3-3_O_Bárbaro.xlsx
+++ b/tabelas_classes_excel/Tabela_3-3_O_Bárbaro.xlsx
@@ -911,9 +911,6 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr"/>
-    </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
@@ -1550,9 +1547,6 @@
           <t>um aprendiz poderia conhecer os bardos</t>
         </is>
       </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -1684,7 +1678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L178"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1737,31 +1731,6 @@
           <t>C7</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>C8</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>C10</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>C11</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>C12</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1773,20 +1742,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nível Bônus Base de Ataque Fortitude</t>
+          <t>Nível</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Bônus Base de Ataque</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fortitude</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>Reflexos</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Vontade</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Especial</t>
         </is>
@@ -2429,1411 +2408,6 @@
       <c r="F23" t="inlineStr">
         <is>
           <t>Fúria poderosa, fúria 6/dia</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>quando estiver usando armadura leve ou não estiver usando armadura. Caso esteja</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Fúria Maior (Ext): No 11°</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>usando uma armadura média ou portando uma carga média, seu deslocamento</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>durante a fúria aumenta para +</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>será reduzido para 9 m. Um bárbaro halfling teria 9 m de deslocamento em vez</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Vontade para +3. A penalidade</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>de 6 m, novamente apenas com uma armadura leve ou sem armadura. Caso esteja</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Vontade Inabalável (Ext):</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>usando uma armadura média ou portando uma carga média, seu deslocamento</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ou superior recebe +4 de bônus</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>será reduzido para 6 m.</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>magias de encantamento. Esse b</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Analfabetismo: Os bárbaros são os únicos personagens que não sabem ler e</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>sive o bônus de moral dos test</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>escrever automaticamente. Para adquirir a capacidade de ler e escrever nos idiomas</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>durante a fúria.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>que conheça, o bárbaro deve gastar 2 pontos de perícia.</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Fúria Incansável (Ext): A</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Um bárbaro que adquirir um nível em qualquer outra classe automaticamente</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>quando sua fúria terminar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>aprenderá a Ler e Escrever. Qualquer outro personagem que escolha um nível de</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Fúria Poderosa (Ext): A p</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>bárbaro não perderá sua alfabetização.</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>bárbaro durante a fúria aument</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Fúria (Ext): Um bárbaro é capaz de mergulhar em uma fúria sanguinária</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>de Vontade para +4. A penalida</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>uma determinada quantidade de vezes a cada dia. Enquanto estiver em fúria, ele</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>adquire força e resistência fenomenais, mas se torna inconseqüente e menos capaz</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Ex-Bárbaros</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>de defender a si mesmo. O personagem recebe, temporariamente, +4 de bônus de</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Um bárbaro que se torne L</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Força e Constituição e +2 de bônus de moral nos testes de resistência de Vontade,</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>níveis adicionais nessa classe</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>mas sofre -2 de penalidade na Classe de Armadura.</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>ção de dano, movimento rápido,</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>A alteração da Constituição aumenta a quantidade de pontos de vida do</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>bárbaro em 2 pontos por nível, mas esses pontos de vida desaparecem quando a</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Conjunto Inicial para Bárbaro</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>fúria terminar e o valor de Constituição do personagem voltar ao normal (esses</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Armadura: Corselete de co</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>pontos de vida adicionais não são eliminados primeiro, de forma semelhante aos</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>12 m de deslocamento, 10 kg).</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>pontos de vida temporários; consulte Pontos de Vida Temporários). Enquanto</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Armas: Machado grande (ld</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>estiver em fúria, um bárbaro não conseguirá utilizar nenhuma perícia baseada em</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Arco curto (ld6, dec. x3,</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Carisma, Destreza ou Inteligência (exceto Equilíbrio, Arte da Fuga, Intimidação</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Adaga (ld4, dec. 19-20/x2</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>e Cavalgar), a perícia Concentração, nem qualquer habilidade que exija paciência</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Seleção de Perícias: Esco</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>ou concentração. Ele também não pode conjurar magias ou utilizar itens mágicos</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>a 4 + modificador de Inteligên</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>acionados com palavras de comando, gatilhos de magia (como uma varinha) ou</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>complementos de magia (como um pergaminho). Um bárbaro em fúria será capaz</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Perícia</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Gradu</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>de usar qualquer talento que tenha, exceto Especialização em Combate, talentos de</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Cavalgar</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>criação de itens ou metamágicos. A fúria permanece ativa durante uma quantidade</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Escalar</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>de rodadas equivalente a 3 + o modificador de Constituição (recém-ajustado) do</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>personagem. O bárbaro consegue terminar sua fúria prematuramente. Quando voltar</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Intimidação</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>ao normal, o bárbaro perderá os modificadores e restrições relacionadas com a fúria</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Natação</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>e ficará exausto (-2 de Força, -2 de Destreza, incapaz de correr) durante o resto do</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Observar (oc)</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>combate (a menos que seja um bárbaro de 17° nível, quando essa limitação não se</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Ouvir</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>aplica mais; veja a seguir).</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Saltar</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>O bárbaro somente poderá entrar em fúria uma vez por combate. No 1° nível,</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>ele consegue ativar essa habilidade uma vez a cada dia. No 4° nível, e a cada 4 níveis</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Sobrevivência</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>subseqüentes, ele poderá ativá-la uma vez adicional por dia (limitado a 6 vezes por dia</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>no 20° nível). Acionar a fúria não consome tempo, mas o bárbaro apenas será capaz</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Talento: Foco em Arma (ma</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>de fazê-lo durante sua ação (veja Iniciativa), nunca em resposta a uma ação alheia.</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Equipamento: Mochila com</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Por exemplo, um bárbaro não poderia ativar a fúria depois de ser atingido por uma</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>sacola, pederneira e isqueiro.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>flecha, para aproveitar os pontos de vida adicionais do aumento de Constituição;</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Dinheiro: 2d4 PO.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>no entanto, esses pontos de vida o beneficiariam caso já estivesse em fúria na rodada</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>anterior e então fosse alvejado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Esquiva Sobrenatural (Ext): A partir do 2° nível, o bárbaro adquire a habilidade</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>intuitiva de reagir ao perigo antes que seus sentidos consigam identificar a ameaça.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Todos sabem que a música</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Ele conserva seu bônus de Destreza na CA (se houver), mesmo em situações de</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>é verdade. Viajar pelo mundo,</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>surpresa ou contra ataques de um oponente invisível. No entanto, ele ainda perde</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>mágica da sua música e sobrevi</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>seu bônus de Destreza na CA quando estiver imobilizado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>um bardo. Quando a sorte ou a</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Caso o bárbaro tenha a habilidade esquiva sobrenatural de uma classe diferente</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>servem como diplomatas, negoci</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>(como um bárbaro com quatro níveis de ladino, por exemplo), ele automaticamente</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>A magia do bardo provém</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>adquire esquiva sobrenatural aprimorada (descrita abaixo).</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>carrega esperança e coragem pa</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Sentir Armadilhas (Ext): A partir do 3° nível, o bárbaro adquire um senso</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>e sua magia para frustrar os p</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>intuitivo que o adverte do perigo das armadilhas, concedendo +1 de bônus nos</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>corruptos, um bardo bondoso se</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>testes de resistência de Reflexos realizados para evitar armadilhas e +1 de bônus de</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>perspicácia e elevando a moral</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>esquiva na CA contra ataques desferidos por armadilhas. Esse bônus aumenta em</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>em um coração maligno. Os bard</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>+1 a cada três níveis subseqüentes (6°, 9°, 12°, 15° e 18° nível). A habilidade sentir</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>tuta da violência, dominando a</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>armadilhas de diversas classes se acumula.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>os presentes que a audiência o</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Esquiva Sobrenatural Aprimorada (Ext): A partir do 5° nível, o bárbaro não</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Aventuras: Os bardos con</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>poderá mais ser flanqueado, pois reagirá aos adversários das suas laterais com a</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>zado. Eles praticam suas períc</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>mesma facilidade que reagiria a somente um atacante. Essa defesa impede que um</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>chance de explorar tumbas anti</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>ladino realize um ataque furtivo quando estiver flanqueando um bárbaro, a menos</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>ancestrais de magia, decifrar</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>que o ladino tenha (no mínimo) 4 níveis de ladino acima do nível de classe atual</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>criaturas exóticas e aprender</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>do bárbaro.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>heróis (ou vilões), unindo-se</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Caso o bárbaro tenha a habilidade esquiva sobrenatural de uma classe diferente</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>em primeira mão – um bardo que</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>(veja acima), ele automaticamente adquire esquiva sobrenatural aprimorada. Os</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>de experiências próprias adqui</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>níveis das classes que concedem a esquiva sobrenatural se acumulam para determinar</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>narrar tantas histórias sobre</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>o nível mínimo dos ladinos capazes de flanquear o personagem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>começam a torná-las para si e</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Redução de Dano (Ext): A partir do 7° nível, o bárbaro adquire a habilidade</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Características: Um bard</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>extraordinária de ignorar parte do dano de cada golpe ou ataque que sofre. Reduza</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>capaz de conjurar somente uma</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>o dano causado em 1 ponto sempre que o bárbaro sofrer um ataque de uma arma ou</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>sem selecioná-las ou prepará-l</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>ataque natural. No 10° nível, e a cada três níveis subseqüentes (13°, 16° e 19° nível),</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>as ilusões, em detrimento das</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>a redução de dano aumenta em 1 ponto. A redução de dano é capaz de reduzir o</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>com freqüência.</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>dano a 0, mas nunca a um valor negativo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Além das magias, o bardo também retira mágica de sua música e poesia. Ele</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>têm dificuldade para se adaptar à</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>é capaz de encorajar seus aliados, manter sua audiência enfeitiçada e anular efeitos</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>exigências desta carreira. Não ex</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>mágicos que dependam de idioma ou do som.</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>anões ou halflings, embora alguns</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Os bardos possuem algumas das perícias dos ladinos, mas não se dedicam com</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>professores dispostos a treiná-lo</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>tanto afinco a dominar essas habilidades como os ladinos. É claro que os bardos</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Os bardos são definitivament</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>ouvem e contam histórias, portanto adquirem um vasto conhecimento de eventos</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>os centauros. Algumas vezes, os b</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>locais e itens famosos ou notáveis.</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>outros humanóides.</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Tendência: Os bardos são viajantes, guiados por sua intuição e vontade, não</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Outras Classes: Um bardo é u</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>pela tradição e pela ordem. O talento espontâneo, a magia e o estilo de vida dos</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>sempre, ele serve como porta-voz</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>bardos são incompatíveis com a tendência Leal.</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>neficiar todos. Os bardos depende</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Religião: Os bardos reverenciam Fharlanghn (deus das estradas). Algumas</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>sem magos ou feiticeir</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>vezes, eles acampam perto de seus templos, na esperança de obter algum dinheiro</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>com os viajantes que param para realizar oferendas à divindade. Alguns bardos,</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Gimble</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>mesmo que não sejam elfos, veneram Corellon Larethian, deus dos elfos e</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>patrono da poesia e da música. Os bardos bondosos também adoram Pelor</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>(deus do sol), e acreditam que ele os protege durante suas viagens. Os bardos</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>relacionados ao caos e indiretamente ao furto veneram Olidammara (deusa dos</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>ladrões). Os bardos malignos são conhecidos por</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>adorar Erythnul (deus da matança), embora poucos</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>admitam sua crença. Os bardos gastam a maior parte</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>de sua vida na estrada e, mesmo que sejam fiéis a</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>uma divindade, dificilmente serão devotos de um</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>templo em particular.</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>História: Um aprendiz de bardo aprende</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>suas perícias com um único mestre experiente,</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>que ele seguirá e servirá até que esteja pronto para</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>escolher seu próprio caminho. Muitos bardos</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>eram crianças órfãs ou fugitivas que se torna-</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>ram amigas de bardos viajantes, que por sua</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>vez se tornaram seus mentores. Como muitos</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>bardos se congregam em “escolas” informais,</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>um aprendiz poderia conhecer os bardos</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>mais importantes de sua região. Ainda assim,</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>nenhum deles cultiva uma lealdade</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>profunda entre si. Na verdade, alguns</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>são altamente competitivos com outros</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>bardos, zelosos com a sua reputação e</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>defensivos com as áreas que consideram</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>seu território.</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Raças: Normalmente, os bardos</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>são humanos, elfos ou meio-elfos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Os humanos se adaptam com facilidade</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>à vida de viajante e a novas terras e costumes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Os elfos são talentosos na música e na magia,</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>ma</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>então a carreira de bardo é natural para</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Dificulda</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>a raça. O estilo peregrino dos bardos</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>equivale</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>agrada aos meio-elfos, que muitas vezes</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>O Cari</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>são estrangeiros em sua própria terra natal. Os</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>para m</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>meio-orcs, mesmo aqueles criados entre os humanos,</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>T</t>
         </is>
       </c>
     </row>
